--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/region-de-antofagasta.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/region-de-antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3506-625-CM26</t>
+          <t>3834-69-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>TOTALPACK LTDA.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>79.948.840-k</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,6 +569,433 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
+        <v>8655.459999999999</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>812799-105-CM25</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>69.020.400-2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>TCHILECOM</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>77.349.120-8</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>20687.61</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>881-52-CM25</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>72.224.100-2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Zecovery Ltda   -    EXEC</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>38991.88</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1233623-144-CM25</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-04-28</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>VICTORIA SpA</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>76.188.587-1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>29772.05</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1233623-153-CM25</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>VICTORIA SpA</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>76.188.587-1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>383543.33</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2384-113-CM25</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>INGENIERIA Y SISTEMAS COMPUTACIONALES S.A.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>79.560.740-4</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>671227.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2429-2524-CM25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Zecovery Ltda   -    EXEC</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>109466.65</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3506-625-CM26</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>69.020.100-3</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>76.334.381-2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
         <v>7651.56</v>
       </c>
     </row>
